--- a/Docs/revisione_core_options_model2.xlsx
+++ b/Docs/revisione_core_options_model2.xlsx
@@ -2,3073 +2,3070 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Core options" sheetId="1" r:id="Rd70ccc850ecf46ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Core options" sheetId="1" r:id="Re842c198fef34878"/>
   </x:sheets>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:si>
-    <x:t xml:space="preserve">nome gioco</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">file name</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">parametro</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">valore di default</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">valori impostabili</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">in core options</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Air Walkers</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">airwlkrs</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">START BUTTON SELECT</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">START BUTTON</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">START BUTTON</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, SHOT BUTTON</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">PLAYER SELECTION</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">2P SIMULTANEOUS</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">2P SIMULTANEOUS</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, 4P SIMULTANEOUS</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Yes</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ATTRACT SOUND</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">OFF</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">OFF</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, ON</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">GAME DIFFICULTY</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">NORMAL</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">NORMAL</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, HARD, HARDEST, EASIEST, EASY</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">GAME TIME</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">2:00</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">2:00</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, 2:30, 3:00, 3:30, 4:00, 4:30, 5:00, 1:00, 1:30</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">REPLAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ON</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">ON</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, OFF</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">WIN FOR FREE PLAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">CPU YES / VS YES</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">CPU YES / VS YES</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, CPU YES / VS NO, CPU NO / VS NO</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">CHARACTER TYPE</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">NORMAL</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, DEFORMATION</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Behind Enemy Lines</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">bel</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">COIN/CREDIT SETTING</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Setting 1: Chute 1 1C 1C / Chute 2 1C 1C</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">Setting 1: Chute 1 1C 1C / Chute 2 1C 1C</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, Setting 2: Chute 1 1C 1C / Chute 2 1C 2C, Setting 3: Chute 1 1C 1C / Chute 2 1C 3C, Setting 4: Chute 1 1C 1C / Chute 2 1C 4C, Setting 5: Chute 1 1C 1C / Chute 2 1C 5C, Setting 6: Chute 1 1C 2C / Chute 2 1C 2C, Setting 7: Chute 1 1C 2C / Chute 2 1C 5C, Setting 8: Chute 1 1C 3C / Chute 2 1C 3C, Setting 9: Chute 1 1C 4C / Chute 2 1C 4C, Setting 10: Chute 1 1C 5C / Chute 2 1C 5C, Setting 11: Chute 1 1C 6C / Chute 2 1C 6C, Setting 12: Chute 1 2C 1C / Chute 2 2C 1C, Setting 13: Chute 1 2C 1C / Chute 2 1C 1C, Setting 14: Chute 1 2C 1C / Chute 2 1C 2C, Setting 15: Chute 1 2C 3C / Chute 2 2C 3C, Setting 16: Chute 1 2C 3C / Chute 2 1C 3C, Setting 17: Chute 1 3C 1C / Chute 2 3C 1C, Setting 18: Chute 1 4C 1C / Chute 2 4C 1C, Setting 19: Chute 1 4C 5C / Chute 2 4C 5C, Setting 20: Chute 1 4C 5C / Chute 2 1C 1C, Setting 21: Chute 1 5C 1C / Chute 2 5C 1C, Setting 22: Chute 1 5C 2C / Chute 2 1C 1C, Setting 23: Chute 1 5C 3C / Chute 2 5C 3C, Setting 24: Chute 1 5C 3C / Chute 2 1C 3C, Setting 25: Chute 1 5C 6C / Chute 2 5C 6C, Setting 26: Chute 1 5C 6C / Chute 2 1C 1C, Setting 27: Chute 1 FREEPLAY / Chute 2 FREEPLAY</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">START CREDITS</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">1</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">1</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, 2, 3, 4, 5</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">CONTINUE CREDITS</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">COUNTRY</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">U.S.</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">U.S.</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, EXPORT, JAPAN</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ADVERTISE SOUND</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">DIFFICULTY</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">6</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">6</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, 7, 8, 9, 10, 1, 2, 3, 4, 5</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Daytona USA</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">daytona</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">LINK ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">MASTER</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">MASTER</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, SLAVE, SINGLE</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">CAR NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">1</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, 2, 3, 4, 5, 6, 7, 8</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">CABINET</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">TWIN</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">TWIN</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, UPRIGHT, DELUXE</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">JPN</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">JPN</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, EXPORT, USA</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">NORMAL</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, HARD, HARDEST, EASY</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">GAME MODE</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">NORMAL</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, GRAND PRIX, ENDURANCE</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">RIVAL ARROW</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Desert Tank</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">desert</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">Setting 1: Chute 1 1C 1C / Chute 2 1C 1C</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, Setting 2: Chute 1 1C 1C / Chute 2 1C 2C, Setting 3: Chute 1 1C 1C / Chute 2 1C 3C, Setting 4: Chute 1 1C 1C / Chute 2 1C 4C, Setting 5: Chute 1 1C 1C / Chute 2 1C 5C, Setting 6: Chute 1 1C 2C / Chute 2 1C 2C, Setting 7: Chute 1 1C 2C / Chute 2 1C 5C, Setting 8: Chute 1 1C 3C / Chute 2 1C 3C, Setting 9: Chute 1 1C 4C / Chute 2 1C 4C, Setting 10: Chute 1 1C 5C / Chute 2 1C 5C, Setting 11: Chute 1 1C 6C / Chute 2 1C 6C, Setting 12: Chute 1 2C 1C / Chute 2 2C 1C, Setting 13: Chute 1 2C 1C / Chute 2 1C 1C, Setting 14: Chute 1 2C 1C / Chute 2 1C 2C, Setting 17: Chute 1 3C 1C / Chute 2 3C 1C, Setting 18: Chute 1 4C 1C / Chute 2 4C 1C, Setting 21: Chute 1 5C 1C / Chute 2 5C 1C, Setting 27: Chute 1 FREEPLAY / Chute 2 FREEPLAY</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">JAPAN</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">JAPAN</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, U.S., EXPORT</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">DIFFICULTY: DESERT</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">EASY</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">EASY</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, NORMAL, HARD, HARDEST, MONKEY</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">DIFFICULTY: CANYON</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Dead or Alive</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">doa</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">VJCOM SET COUNT</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">2</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">2</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, 3, 4, 5</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">VJMAN SET COUNT</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">VJCOM DIFFICULTY</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">NORMAL</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, EASY, HARD, VERY HARD</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">VJCOM ENERGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">VJMAN ENERGY</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">DEMO SOUND</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">NATION</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">JAPAN</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:color theme="1"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, U.S.A., EXPORT</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">CONTINUE</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">ON</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, OFF</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">V.S FINISH</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">OFF</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">BURST MODE</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">OFF</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, ON</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Dynamite Baseball</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">dynabb</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">NORMAL</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, HARD, HARDEST, EASY</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">CABINET TYPE</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">US</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">US</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, CITY, MEGALO</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">FAVORITE</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">OFF</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, SWALLOWS, CARP, GIANTS, BAYSTARS, DRAGONS, TIGERS, BLUEWAVE, MARINES, LIONS, FIGHTERS, HAWKS, BUFFALOES</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">INNINGS</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">1CREDIT 2INNINGS</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">1CREDIT 2INNINGS</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, 1CREDIT 3INNINGS, 1CREDIT 1INNING / 2CREDITS 3INNINGS / 3CREDITS 5INNINGS / 4CREDITS 9INNINGS, 1CREDIT 2INNINGS / 2CREDITS 5INNINGS / 3CREDITS 9INNINGS, 1CREDIT 1INNING</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Dynamite Baseball 97</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">dynabb97</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">1CREDIT 2INNINGS</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, 1CREDIT 3INNINGS, 1CREDIT 1INNING</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Dynamite Cop</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">dynamcop</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">3</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">3</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, 4, 5, 6, 7, 8, 1, 2</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">LIFE AMOUNT</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">104</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">104</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, 112, 120, 128, 136, 144, 152, 160, 168, 176, 184, 192, 200, 208, 216, 224, 232, 240, 248, 256, 264, 272, 280, 288, 296, 304, 312, 320, 64, 72, 80, 88, 96</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">VIOLENCE MODE</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Fighting Vipers</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">fvipers</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">MATCH COUNT(1P)</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">2</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, 3, 4, 5</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">MATCH COUNT(VS)</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">JAPAN</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, USA, EXPORT</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">DISPLAY TYPE</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">PROJECTOR</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">PROJECTOR</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, C.R.T.</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">VS FINISH</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">RANKING MODE</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Gunblade NY</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">gunblade</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">1/8</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">1/8</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, 2/8, 3/8, 4/8, 5/8, 6/8, 7/8, 8/8</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SHIFTING DIFFICULTY</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">PLAYER LIFE</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">2</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, 3, 4, 5, 6, 7, 8</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">GUN REACTION</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">DX</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">DX</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, SD</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">The House of the Dead</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">hotd</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">NORMAL</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, MEDIUM HARD, VERY HARD, VERY EASY, MEDIUM EASY</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">LIFE SETTING</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">3/5</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">3/5</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, 4/5, 5/5, 1/3, 2/3, 3/3, 1/4, 2/4, 3/4, 4/4, 1/5, 2/5</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">BLOOD COLOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">GREEN</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">GREEN</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, BLUE, PURPLE, RED</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Hanguk Pro Yagu 98</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">hpyagu98</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">OFF</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, GIANTS, EAGLES, UNICORNS, LIONS, RAIDERS, BEARS, TWINS, TIGERS</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">INDY 500 Twin</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">indy500</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">NORMAL</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, HARD, HARDEST, VERY EASY, EASY</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">RACE MODE</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">NORMAL</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, LONG</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">HANDICAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">USA</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">USA</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, EXP, JAPAN</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">TWIN</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, DELUXE</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">NETWORK TYPE</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">STAND ALONE</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">STAND ALONE</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, MASTER, SLAVE</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">CABINET ID</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">1</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, 2, 3, 4, 5, 6, 7, 8</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ENGINE VOLUME</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">1</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, 2, 3</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">DEFAULT VIEW</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">1</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, 2, 3, 4</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Last Bronx</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">lastbrnx</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">1 NORMAL</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">1 NORMAL</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, 2 HARD, 3 HARDEST, 0 EASY</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SURVIVAL MODE</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">MATCH POINT(CPU)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">MATCH POINT(VS)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">CUT CROSS STREET</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">C.R.T.</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">C.R.T.</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, PROJECTOR</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">MASTER VOLUME</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">1</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, 2, 3, 4, 5, 6, 7</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Manx TT Superbike - DX/Twin</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">manxtt</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">DELUXE</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">DELUXE</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, TWIN</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">LINK TYPE</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Not Link</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">Not Link</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, Master, Slave, Relay</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">BIKE COLOR (No.)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">RED (No.1)</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">RED (No.1)</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, BLUE (No.2), YELLOW (No.3), GREEN (No.4), GREEN (No.5), YELLOW (No.6), BLUE (No.7), RED (No.8)</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">RACE</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">RACE</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, T.T.</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">LAXEY NUMBER OF LAP</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">2</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, 3, 4, 5, 6, 7, 8, 9, 10, 1</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">LAXEY GAME DIFFICULTY</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">LAXEY REVISE MODE</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">2/3</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">2/3</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, 3/3, Not Revise, 1/3</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">TT NUMBER OF LAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">TT GAME DIFFICULTY</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">TT REVISE MODE</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">START SWITCH OP.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Motor Raid - Twin</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">motoraid</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">NORMAL</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, HARD, VERY HARD, VERY EASY, EASY</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">STANDARD</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">STANDARD</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, LONG</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ENEMY LEVEL</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">NORMAL</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, STRONG</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">STANDARD</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, HALF</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">JAPAN</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, USA, EXP</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">STAND ALONE</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, MASTER, SLAVE, LIVE</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Over Rev</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">overrev</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">JAPAN</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, U.S.A., EUROPE, KOREA</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">HARDWARE TYPE</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">NORMAL (2in1)</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">NORMAL (2in1)</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, SEGA INDY, SEGA INDY DX / GT24h DX, SEGA STCC</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">LINK MAX</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">NOT LINK</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">NOT LINK</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, 2 LINKS, 3 LINKS, 4 LINKS</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">MASTER CarNo.1</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">MASTER CarNo.1</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, SLAVE CarNo.2, SLAVE CarNo.3, SLAVE CarNo.4</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">TIME DIFFICULTY</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">1</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, 2, 3, 4, 5</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">STEER KICK BACK</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">NORMAL</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, HARD, VERY HARD, EASY</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">MAXIMUM LAP</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">NORMAL MODE</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">NORMAL MODE</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, LONG MODE, VERY LONG MODE</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Pilot Kids</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">pltkids</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Fighters</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">3</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, 4, 5, 1, 2</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Difficult</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Normal</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">Normal</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, Difficult, More Difficult, Easy</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Demo Sound</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Off</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">Off</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, On</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Coin Slot</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Same</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">Same</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, Individual</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Coin Mode</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">Normal</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, Continue Start = 2Coins, Free Play</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Coin-1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">1Coin = 1Credit</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">1Coin = 1Credit</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, 2Coins = 1Credit, 3Coins = 1Credit, 4Coins = 1Credit, 5Coins = 1Credit, 6Coins = 1Credit, 1Coin = 2Credits, 1Coin = 3Credits, 1Coin = 4Credits</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Coin-2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Continue</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">On</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">On</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, Off</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Royal Ascot II</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">rascot2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Nessun parametro acquisito</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Rail Chase 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">rchase2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">10 sec EVERY</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">10 sec EVERY</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, 20 sec EVERY, 30 sec EVERY, 40 sec EVERY, 50 sec EVERY, 60 sec EVERY, 70 sec EVERY, NONE</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Sonic Championship</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">schamp</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ENEMY RANK</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">TIME</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">30</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">30</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, 40, 50, 60, 70, 80, 90, 99, 10, 20</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ENERGY(1P)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ENERGY(VS)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">BARRIER</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">5</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">5</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, 6, 7, 8, 9, 10, 1, 2, 3, 4</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">BARRIER RESET</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">AUTOMATIC</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">HYPER MODE</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">DAMAGE</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">NORMAL</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, REAL</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">USA</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, EXPORT, JAPAN</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Sega Water Ski</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">segawski</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Super GT 24h</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sgt24h</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">NOT LINK</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, CAR NO1 Master, CAR NO2 Slave, CAR NO3 Slave, CAR NO4 Slave</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">2</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, 3, 4</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">JAPAN</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, USA, EUR</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">NORMAL</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, EASY, HARD, HARDEST</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">CPU CAR LEVEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">STEERING FORCE</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">GAME BGM</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">I/O TYPE</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">A</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">A</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, B, C</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Sega Ski Super G</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">skisuprg</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">NO LINK</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">NO LINK</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, MASTER, SLAVE</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">DRIVE BOARD POWER</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">2</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, 3, 4, 1</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">LIVE DISPLAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">VICTORIA DISPLAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">INITIAL TIME</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">10</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">10</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 0, 1, 2, 3, 4, 5, 6, 7, 8, 9</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">STAGE TIME (WHITE FOREST)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">STAGE TIME (NIGHT VALLEY)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">STAGE TIME (WILD KING)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Sky Target</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">skytargt</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">STANDARD</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, DELUXE</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Sega Rally Championship - Twin/DX</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">srallyc</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">JPN</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, USA, EXPORT</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">NOTLINK</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">NOTLINK</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, CAR 1, CAR 2, CAR 3, CAR 4, RELAY</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">NORMAL</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, SHORT, LONG, LONGEST</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Sega Touring Car Championship</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">stcc</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">URL ADDRESS</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">TWIN</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, DELUX</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">STAND ALONE</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, CAR 1, CAR 2, CAR 3, CAR 4, CAR 5, CAR 6, CAR 7, CAR 8, RELAY</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">NORMAL</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, SHORT, LONG, GRAND PRIX</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">DEFAULT CAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">RANDOM</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">RANDOM</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, ALFA ROMEO, MERCEDES, OPEL, TOYOTA</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">NAME ENTRY</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">BEFORE-3</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">BEFORE-3</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, AFTER-3, BEFORE-7, AFTER-7</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">BIRD'S</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">BIRD'S</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, DRIVER'S</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Top Skater</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">topskatr</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">4 / 8</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">4 / 8</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, 5 / 8, 6 / 8, 7 / 8, 8 / 8, 1 / 8, 2 / 8, 3 / 8</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Virtua Cop</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">vcop</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">JPN</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, EXP, USA</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">DX</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, SP U/R, U/R</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">NORMAL</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, MEDIUM HARD, HARD, VERY HARD, HARDEST, EASIEST, VERY EASY, EASY, MEDIUM EASY</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">LIFE</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">1</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, 2, 3, 4, 5, 6, 7, 8, 9</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Virtua Cop 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">vcop2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Virtua Fighter 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">vf2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">DRINK</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">OK</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">OK</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, NG</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">VERSION</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">NORMAL</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, VERSION 2</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Cyber Troopers Virtual-On - Twin</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">von</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">PLAY TIME 1P (STAGE 1~5)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">30 SECS</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">30 SECS</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, 35 SECS, 40 SECS, 45 SECS, 50 SECS, 55 SECS, 60 SECS, 65 SECS, 70 SECS, 75 SECS, 80 SECS, 85 SECS, 90 SECS, 95 SECS, DEATH-MATCH</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">PLAY TIME 1P (PENALTY)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">PLAY TIME 1P (STAGE 6~8)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">PLAY TIME 1P (LAST STG)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">90 SECS</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">90 SECS</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, 95 SECS, DEATH-MATCH</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">PLAY TIME VERSUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">MATCH COUNT 1P (STAGE 1~5)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">MATCH COUNT 1P (PENALTY)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">MATCH COUNT 1P (STAGE 6~8)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">MATCH COUNT VERSUS</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">NETWORK LINK ATTRIBUTE</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">NO LINK</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, SLAVE, MASTER</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">WINNING BY DECISION</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">LOUD</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">LOUD</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, OFF, SOFT</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">REPLAY AND POSING MODE</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">REPLAY&amp;POSING</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">REPLAY&amp;POSING</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, NONE, REPLAY ONLY, POSING ONLY</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">VERSUS ALWAYS FINISH</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">DISPLAY BRIGHTNESS</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">0</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">0</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, +1, +2, +3, +4, +5, -5, -4, -3, -2, -1</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Virtua Striker</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">vstriker</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">MONITOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">CRT</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">CRT</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, PROJECTER</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">TIME SET</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">2:00</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, 2:15, 2:30, 2:45, 3:00, 1:15, 1:30, 1:45</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">V GOAL SYSTEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">V GOAL TIME SET</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">0:15</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">0:15</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, 0:30, 0:45, 1:00, TIME FREE</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">PK SYSTEM</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">PK MEMBER SET</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">3</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, 4, 5, REAL PK</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">BILLBOARD</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ONE MATCH MODE</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Wave Runner</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">waverunr</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Zero Gunner (zerogun)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">zerogun</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Credit Mode</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Continue Mode</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Normal Mode</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">Normal Mode</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, Free Play Mode</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Coin Slot 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">1 coin(s) 1 credit(s)</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">1 coin(s) 1 credit(s)</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, 2 coin(s) 1 credit(s), 3 coin(s) 1 credit(s), 1 coin(s) 2 credit(s), 1 coin(s) 3 credit(s), 1 coin(s) 4 credit(s), 1 coin(s) 5 credit(s), 1 coin(s) 6 credit(s)</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Coin Slot 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Difficulty</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">EASY</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, NORMAL, HARD, VERY HARD</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">1 fighter</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">1 fighter</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, 2 fighters, 3 fighters, 4 fighters</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Extend Points</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">600000</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">600000</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, 800000</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Ranking Data</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Do Initialize</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:b/>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">Do Initialize</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Aptos"/>
-      </x:rPr>
-      <x:t xml:space="preserve">, Do NOT Initialize</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Zero Gunner (zeroguna)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">zeroguna</x:t>
-  </x:si>
-</x:sst>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <si>
+    <t xml:space="preserve">nome gioco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">file name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parametro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">valore di default</t>
+  </si>
+  <si>
+    <t xml:space="preserve">valori impostabili</t>
+  </si>
+  <si>
+    <t xml:space="preserve">in core options</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Air Walkers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">airwlkrs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">START BUTTON SELECT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">START BUTTON</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">START BUTTON</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, SHOT BUTTON</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">PLAYER SELECTION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2P SIMULTANEOUS</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">2P SIMULTANEOUS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, 4P SIMULTANEOUS</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATTRACT SOUND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OFF</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">OFF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, ON</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">GAME DIFFICULTY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORMAL</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">NORMAL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, HARD, HARDEST, EASIEST, EASY</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">GAME TIME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2:00</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">2:00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, 2:30, 3:00, 3:30, 4:00, 4:30, 5:00, 1:00, 1:30</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">REPLAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ON</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">ON</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, OFF</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">WIN FOR FREE PLAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CPU YES / VS YES</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">CPU YES / VS YES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, CPU YES / VS NO, CPU NO / VS NO</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">CHARACTER TYPE</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">NORMAL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, DEFORMATION</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Behind Enemy Lines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COIN/CREDIT SETTING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setting 1: Chute 1 1C 1C / Chute 2 1C 1C</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">Setting 1: Chute 1 1C 1C / Chute 2 1C 1C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, Setting 2: Chute 1 1C 1C / Chute 2 1C 2C, Setting 3: Chute 1 1C 1C / Chute 2 1C 3C, Setting 4: Chute 1 1C 1C / Chute 2 1C 4C, Setting 5: Chute 1 1C 1C / Chute 2 1C 5C, Setting 6: Chute 1 1C 2C / Chute 2 1C 2C, Setting 7: Chute 1 1C 2C / Chute 2 1C 5C, Setting 8: Chute 1 1C 3C / Chute 2 1C 3C, Setting 9: Chute 1 1C 4C / Chute 2 1C 4C, Setting 10: Chute 1 1C 5C / Chute 2 1C 5C, Setting 11: Chute 1 1C 6C / Chute 2 1C 6C, Setting 12: Chute 1 2C 1C / Chute 2 2C 1C, Setting 13: Chute 1 2C 1C / Chute 2 1C 1C, Setting 14: Chute 1 2C 1C / Chute 2 1C 2C, Setting 15: Chute 1 2C 3C / Chute 2 2C 3C, Setting 16: Chute 1 2C 3C / Chute 2 1C 3C, Setting 17: Chute 1 3C 1C / Chute 2 3C 1C, Setting 18: Chute 1 4C 1C / Chute 2 4C 1C, Setting 19: Chute 1 4C 5C / Chute 2 4C 5C, Setting 20: Chute 1 4C 5C / Chute 2 1C 1C, Setting 21: Chute 1 5C 1C / Chute 2 5C 1C, Setting 22: Chute 1 5C 2C / Chute 2 1C 1C, Setting 23: Chute 1 5C 3C / Chute 2 5C 3C, Setting 24: Chute 1 5C 3C / Chute 2 1C 3C, Setting 25: Chute 1 5C 6C / Chute 2 5C 6C, Setting 26: Chute 1 5C 6C / Chute 2 1C 1C, Setting 27: Chute 1 FREEPLAY / Chute 2 FREEPLAY</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">START CREDITS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, 2, 3, 4, 5</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTINUE CREDITS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COUNTRY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U.S.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">U.S.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, EXPORT, JAPAN</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ADVERTISE SOUND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIFFICULTY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, 7, 8, 9, 10, 1, 2, 3, 4, 5</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Daytona USA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">daytona</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LINK ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MASTER</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">MASTER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, SLAVE, SINGLE</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">CAR NUMBER</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, 2, 3, 4, 5, 6, 7, 8</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">CABINET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TWIN</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">TWIN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, UPRIGHT, DELUXE</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">JPN</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">JPN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, EXPORT, USA</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">NORMAL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, HARD, HARDEST, EASY</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">GAME MODE</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">NORMAL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, GRAND PRIX, ENDURANCE</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">RIVAL ARROW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desert Tank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">desert</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">Setting 1: Chute 1 1C 1C / Chute 2 1C 1C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, Setting 2: Chute 1 1C 1C / Chute 2 1C 2C, Setting 3: Chute 1 1C 1C / Chute 2 1C 3C, Setting 4: Chute 1 1C 1C / Chute 2 1C 4C, Setting 5: Chute 1 1C 1C / Chute 2 1C 5C, Setting 6: Chute 1 1C 2C / Chute 2 1C 2C, Setting 7: Chute 1 1C 2C / Chute 2 1C 5C, Setting 8: Chute 1 1C 3C / Chute 2 1C 3C, Setting 9: Chute 1 1C 4C / Chute 2 1C 4C, Setting 10: Chute 1 1C 5C / Chute 2 1C 5C, Setting 11: Chute 1 1C 6C / Chute 2 1C 6C, Setting 12: Chute 1 2C 1C / Chute 2 2C 1C, Setting 13: Chute 1 2C 1C / Chute 2 1C 1C, Setting 14: Chute 1 2C 1C / Chute 2 1C 2C, Setting 17: Chute 1 3C 1C / Chute 2 3C 1C, Setting 18: Chute 1 4C 1C / Chute 2 4C 1C, Setting 21: Chute 1 5C 1C / Chute 2 5C 1C, Setting 27: Chute 1 FREEPLAY / Chute 2 FREEPLAY</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">JAPAN</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">JAPAN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, U.S., EXPORT</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">DIFFICULTY: DESERT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EASY</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">EASY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, NORMAL, HARD, HARDEST, MONKEY</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">DIFFICULTY: CANYON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dead or Alive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">doa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VJCOM SET COUNT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, 3, 4, 5</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">VJMAN SET COUNT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VJCOM DIFFICULTY</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">NORMAL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, EASY, HARD, VERY HARD</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">VJCOM ENERGY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VJMAN ENERGY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEMO SOUND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NATION</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">JAPAN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, U.S.A., EXPORT</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTINUE</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">ON</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, OFF</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">V.S FINISH</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">OFF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">BURST MODE</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">OFF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, ON</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Dynamite Baseball</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dynabb</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">NORMAL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, HARD, HARDEST, EASY</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">CABINET TYPE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">US</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, CITY, MEGALO</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">FAVORITE</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">OFF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, SWALLOWS, CARP, GIANTS, BAYSTARS, DRAGONS, TIGERS, BLUEWAVE, MARINES, LIONS, FIGHTERS, HAWKS, BUFFALOES</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">INNINGS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1CREDIT 2INNINGS</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">1CREDIT 2INNINGS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, 1CREDIT 3INNINGS, 1CREDIT 1INNING / 2CREDITS 3INNINGS / 3CREDITS 5INNINGS / 4CREDITS 9INNINGS, 1CREDIT 2INNINGS / 2CREDITS 5INNINGS / 3CREDITS 9INNINGS, 1CREDIT 1INNING</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Dynamite Baseball 97</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dynabb97</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">1CREDIT 2INNINGS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, 1CREDIT 3INNINGS, 1CREDIT 1INNING</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Dynamite Cop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dynamcop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, 4, 5, 6, 7, 8, 1, 2</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">LIFE AMOUNT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">104</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, 112, 120, 128, 136, 144, 152, 160, 168, 176, 184, 192, 200, 208, 216, 224, 232, 240, 248, 256, 264, 272, 280, 288, 296, 304, 312, 320, 64, 72, 80, 88, 96</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">VIOLENCE MODE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fighting Vipers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fvipers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATCH COUNT(1P)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, 3, 4, 5</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">MATCH COUNT(VS)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">JAPAN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, USA, EXPORT</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">DISPLAY TYPE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROJECTOR</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">PROJECTOR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, C.R.T.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">VS FINISH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RANKING MODE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gunblade NY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gunblade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1/8</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">1/8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, 2/8, 3/8, 4/8, 5/8, 6/8, 7/8, 8/8</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">SHIFTING DIFFICULTY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLAYER LIFE</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, 3, 4, 5, 6, 7, 8</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">GUN REACTION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DX</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">DX</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, SD</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">The House of the Dead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hotd</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">NORMAL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, MEDIUM HARD, VERY HARD, VERY EASY, MEDIUM EASY</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">LIFE SETTING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/5</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">3/5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, 4/5, 5/5, 1/3, 2/3, 3/3, 1/4, 2/4, 3/4, 4/4, 1/5, 2/5</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">BLOOD COLOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GREEN</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">GREEN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, BLUE, PURPLE, RED</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Hanguk Pro Yagu 98</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hpyagu98</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">OFF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, GIANTS, EAGLES, UNICORNS, LIONS, RAIDERS, BEARS, TWINS, TIGERS</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">INDY 500 Twin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">indy500</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">NORMAL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, HARD, HARDEST, VERY EASY, EASY</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">RACE MODE</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">NORMAL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, LONG</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">HANDICAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USA</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">USA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, EXP, JAPAN</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">TWIN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, DELUXE</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">NETWORK TYPE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STAND ALONE</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">STAND ALONE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, MASTER, SLAVE</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">CABINET ID</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, 2, 3, 4, 5, 6, 7, 8</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ENGINE VOLUME</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, 2, 3</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">DEFAULT VIEW</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, 2, 3, 4</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Last Bronx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lastbrnx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 NORMAL</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">1 NORMAL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, 2 HARD, 3 HARDEST, 0 EASY</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">SURVIVAL MODE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATCH POINT(CPU)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATCH POINT(VS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUT CROSS STREET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C.R.T.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">C.R.T.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, PROJECTOR</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">MASTER VOLUME</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, 2, 3, 4, 5, 6, 7</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Manx TT Superbike - DX/Twin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manxtt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELUXE</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">DELUXE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, TWIN</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">LINK TYPE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not Link</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">Not Link</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, Master, Slave, Relay</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">BIKE COLOR (No.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RED (No.1)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">RED (No.1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, BLUE (No.2), YELLOW (No.3), GREEN (No.4), GREEN (No.5), YELLOW (No.6), BLUE (No.7), RED (No.8)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">RACE</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">RACE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, T.T.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">LAXEY NUMBER OF LAP</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, 3, 4, 5, 6, 7, 8, 9, 10, 1</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">LAXEY GAME DIFFICULTY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAXEY REVISE MODE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2/3</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">2/3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, 3/3, Not Revise, 1/3</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">TT NUMBER OF LAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TT GAME DIFFICULTY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TT REVISE MODE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">START SWITCH OP.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motor Raid - Twin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">motoraid</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">NORMAL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, HARD, VERY HARD, VERY EASY, EASY</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">STANDARD</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">STANDARD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, LONG</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ENEMY LEVEL</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">NORMAL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, STRONG</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">STANDARD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, HALF</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">JAPAN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, USA, EXP</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">STAND ALONE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, MASTER, SLAVE, LIVE</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Over Rev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">overrev</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">JAPAN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, U.S.A., EUROPE, KOREA</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">HARDWARE TYPE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORMAL (2in1)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">NORMAL (2in1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, SEGA INDY, SEGA INDY DX / GT24h DX, SEGA STCC</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">LINK MAX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOT LINK</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">NOT LINK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, 2 LINKS, 3 LINKS, 4 LINKS</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">MASTER CarNo.1</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">MASTER CarNo.1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, SLAVE CarNo.2, SLAVE CarNo.3, SLAVE CarNo.4</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">TIME DIFFICULTY</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, 2, 3, 4, 5</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">STEER KICK BACK</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">NORMAL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, HARD, VERY HARD, EASY</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">MAXIMUM LAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORMAL MODE</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">NORMAL MODE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, LONG MODE, VERY LONG MODE</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Pilot Kids</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pltkids</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fighters</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, 4, 5, 1, 2</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Difficult</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Normal</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">Normal</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, Difficult, More Difficult, Easy</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Demo Sound</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Off</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">Off</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, On</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Coin Slot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">Same</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, Individual</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Coin Mode</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">Normal</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, Continue Start = 2Coins, Free Play</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Coin-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1Coin = 1Credit</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">1Coin = 1Credit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, 2Coins = 1Credit, 3Coins = 1Credit, 4Coins = 1Credit, 5Coins = 1Credit, 6Coins = 1Credit, 1Coin = 2Credits, 1Coin = 3Credits, 1Coin = 4Credits</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Coin-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Continue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">On</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, Off</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Royal Ascot II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rascot2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nessun parametro acquisito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rail Chase 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rchase2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 sec EVERY</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">10 sec EVERY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, 20 sec EVERY, 30 sec EVERY, 40 sec EVERY, 50 sec EVERY, 60 sec EVERY, 70 sec EVERY, NONE</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Sonic Championship</t>
+  </si>
+  <si>
+    <t xml:space="preserve">schamp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENEMY RANK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TIME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, 40, 50, 60, 70, 80, 90, 99, 10, 20</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ENERGY(1P)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENERGY(VS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BARRIER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, 6, 7, 8, 9, 10, 1, 2, 3, 4</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">BARRIER RESET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AUTOMATIC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYPER MODE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DAMAGE</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">NORMAL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, REAL</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">USA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, EXPORT, JAPAN</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Sega Water Ski</t>
+  </si>
+  <si>
+    <t xml:space="preserve">segawski</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Super GT 24h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sgt24h</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">NOT LINK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, CAR NO1 Master, CAR NO2 Slave, CAR NO3 Slave, CAR NO4 Slave</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, 3, 4</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">JAPAN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, USA, EUR</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">NORMAL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, EASY, HARD, HARDEST</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">CPU CAR LEVEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STEERING FORCE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAME BGM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I/O TYPE</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">A, B, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Sega Ski Super G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skisuprg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NO LINK</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">NO LINK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, MASTER, SLAVE</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">DRIVE BOARD POWER</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, 3, 4, 1</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">LIVE DISPLAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VICTORIA DISPLAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INITIAL TIME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 0, 1, 2, 3, 4, 5, 6, 7, 8, 9</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">STAGE TIME (WHITE FOREST)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STAGE TIME (NIGHT VALLEY)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STAGE TIME (WILD KING)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sky Target</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skytargt</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">STANDARD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, DELUXE</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Sega Rally Championship - Twin/DX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">srallyc</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">JPN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, USA, EXPORT</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">NOTLINK</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">NOTLINK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, CAR 1, CAR 2, CAR 3, CAR 4, RELAY</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">NORMAL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, SHORT, LONG, LONGEST</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Sega Touring Car Championship</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stcc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL ADDRESS</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">TWIN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, DELUX</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">STAND ALONE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, CAR 1, CAR 2, CAR 3, CAR 4, CAR 5, CAR 6, CAR 7, CAR 8, RELAY</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">NORMAL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, SHORT, LONG, GRAND PRIX</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">DEFAULT CAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RANDOM</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">RANDOM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, ALFA ROMEO, MERCEDES, OPEL, TOYOTA</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">NAME ENTRY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEFORE-3</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">BEFORE-3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, AFTER-3, BEFORE-7, AFTER-7</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">BIRD'S</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">BIRD'S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, DRIVER'S</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Top Skater</t>
+  </si>
+  <si>
+    <t xml:space="preserve">topskatr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 / 8</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">4 / 8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, 5 / 8, 6 / 8, 7 / 8, 8 / 8, 1 / 8, 2 / 8, 3 / 8</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtua Cop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vcop</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">JPN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, EXP, USA</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">DX</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, SP U/R, U/R</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">NORMAL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, MEDIUM HARD, HARD, VERY HARD, HARDEST, EASIEST, VERY EASY, EASY, MEDIUM EASY</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">LIFE</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, 2, 3, 4, 5, 6, 7, 8, 9</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtua Cop 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vcop2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtua Fighter 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vf2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRINK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OK</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">OK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, NG</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">VERSION</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">NORMAL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, VERSION 2</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyber Troopers Virtual-On - Twin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">von</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLAY TIME 1P (STAGE 1~5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 SECS</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">30 SECS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, 35 SECS, 40 SECS, 45 SECS, 50 SECS, 55 SECS, 60 SECS, 65 SECS, 70 SECS, 75 SECS, 80 SECS, 85 SECS, 90 SECS, 95 SECS, DEATH-MATCH</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">PLAY TIME 1P (PENALTY)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLAY TIME 1P (STAGE 6~8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLAY TIME 1P (LAST STG)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90 SECS</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">90 SECS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, 95 SECS, DEATH-MATCH</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">PLAY TIME VERSUS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATCH COUNT 1P (STAGE 1~5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATCH COUNT 1P (PENALTY)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATCH COUNT 1P (STAGE 6~8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATCH COUNT VERSUS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NETWORK LINK ATTRIBUTE</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">NO LINK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, SLAVE, MASTER</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">WINNING BY DECISION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOUD</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">LOUD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, OFF, SOFT</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">REPLAY AND POSING MODE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REPLAY&amp;POSING</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">REPLAY&amp;POSING</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, NONE, REPLAY ONLY, POSING ONLY</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">VERSUS ALWAYS FINISH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DISPLAY BRIGHTNESS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, +1, +2, +3, +4, +5, -5, -4, -3, -2, -1</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtua Striker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vstriker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MONITOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRT</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">CRT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, PROJECTER</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">TIME SET</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">2:00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, 2:15, 2:30, 2:45, 3:00, 1:15, 1:30, 1:45</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">V GOAL SYSTEM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V GOAL TIME SET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0:15</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">0:15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, 0:30, 0:45, 1:00, TIME FREE</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">PK SYSTEM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PK MEMBER SET</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, 4, 5, REAL PK</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">BILLBOARD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ONE MATCH MODE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wave Runner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">waverunr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zero Gunner (zerogun)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zerogun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Credit Mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Continue Mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Normal Mode</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">Normal Mode</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, Free Play Mode</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Coin Slot 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 coin(s) 1 credit(s)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">1 coin(s) 1 credit(s)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, 2 coin(s) 1 credit(s), 3 coin(s) 1 credit(s), 1 coin(s) 2 credit(s), 1 coin(s) 3 credit(s), 1 coin(s) 4 credit(s), 1 coin(s) 5 credit(s), 1 coin(s) 6 credit(s)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Coin Slot 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Difficulty</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">EASY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, NORMAL, HARD, VERY HARD</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">1 fighter</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">1 fighter</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, 2 fighters, 3 fighters, 4 fighters</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Extend Points</t>
+  </si>
+  <si>
+    <t xml:space="preserve">600000</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">600000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, 800000</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Ranking Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Do Initialize</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">Do Initialize</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos"/>
+      </rPr>
+      <t xml:space="preserve">, Do NOT Initialize</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Zero Gunner (zeroguna)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zeroguna</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3136,7 +3133,7 @@
         <x:name val="Aptos"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor auto="1"/>
         </x:patternFill>
       </x:fill>
@@ -3148,7 +3145,7 @@
         <x:name val="Aptos"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor auto="1"/>
         </x:patternFill>
       </x:fill>
@@ -3160,7 +3157,7 @@
         <x:name val="Aptos"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor auto="1"/>
         </x:patternFill>
       </x:fill>
@@ -3172,7 +3169,7 @@
         <x:name val="Aptos"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor auto="1"/>
         </x:patternFill>
       </x:fill>
@@ -3184,7 +3181,7 @@
         <x:name val="Aptos"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor auto="1"/>
         </x:patternFill>
       </x:fill>
@@ -3196,7 +3193,7 @@
         <x:name val="Aptos"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor auto="1"/>
         </x:patternFill>
       </x:fill>
@@ -3208,7 +3205,7 @@
         <x:name val="Aptos"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor auto="1"/>
         </x:patternFill>
       </x:fill>
@@ -3219,7 +3216,7 @@
         <x:color auto="1"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor auto="1"/>
         </x:patternFill>
       </x:fill>
@@ -6786,22 +6783,22 @@
       <x:c r="C168" s="1" t="s">
         <x:v>284</x:v>
       </x:c>
-      <x:c r="D168" s="1" t="s">
+      <x:c r="D168" s="1" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="E168" s="1" t="s">
         <x:v>285</x:v>
       </x:c>
-      <x:c r="E168" s="1" t="s">
-        <x:v>286</x:v>
-      </x:c>
       <x:c r="F168" s="2" t="str">
-        <x:f>""</x:f>
+        <x:v>Yes</x:v>
       </x:c>
     </x:row>
     <x:row r="169" ht="15" customHeight="1">
       <x:c r="A169" s="1" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="B169" s="1" t="s">
         <x:v>287</x:v>
-      </x:c>
-      <x:c r="B169" s="1" t="s">
-        <x:v>288</x:v>
       </x:c>
       <x:c r="C169" s="1" t="s">
         <x:v>44</x:v>
@@ -6818,10 +6815,10 @@
     </x:row>
     <x:row r="170" ht="15" customHeight="1">
       <x:c r="A170" s="1" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="B170" s="1" t="s">
         <x:v>287</x:v>
-      </x:c>
-      <x:c r="B170" s="1" t="s">
-        <x:v>288</x:v>
       </x:c>
       <x:c r="C170" s="1" t="s">
         <x:v>41</x:v>
@@ -6838,19 +6835,19 @@
     </x:row>
     <x:row r="171" ht="15" customHeight="1">
       <x:c r="A171" s="1" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="B171" s="1" t="s">
         <x:v>287</x:v>
-      </x:c>
-      <x:c r="B171" s="1" t="s">
-        <x:v>288</x:v>
       </x:c>
       <x:c r="C171" s="1" t="s">
         <x:v>156</x:v>
       </x:c>
       <x:c r="D171" s="1" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="E171" s="1" t="s">
         <x:v>289</x:v>
-      </x:c>
-      <x:c r="E171" s="1" t="s">
-        <x:v>290</x:v>
       </x:c>
       <x:c r="F171" s="2" t="s">
         <x:v>14</x:v>
@@ -6858,10 +6855,10 @@
     </x:row>
     <x:row r="172" ht="15" customHeight="1">
       <x:c r="A172" s="1" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="B172" s="1" t="s">
         <x:v>287</x:v>
-      </x:c>
-      <x:c r="B172" s="1" t="s">
-        <x:v>288</x:v>
       </x:c>
       <x:c r="C172" s="1" t="s">
         <x:v>159</x:v>
@@ -6878,31 +6875,31 @@
     </x:row>
     <x:row r="173" ht="15" customHeight="1">
       <x:c r="A173" s="1" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="B173" s="1" t="s">
         <x:v>287</x:v>
       </x:c>
-      <x:c r="B173" s="1" t="s">
-        <x:v>288</x:v>
-      </x:c>
       <x:c r="C173" s="1" t="s">
-        <x:v>291</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="D173" s="1" t="s">
         <x:v>76</x:v>
       </x:c>
       <x:c r="E173" s="1" t="s">
-        <x:v>292</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="F173" s="2"/>
     </x:row>
     <x:row r="174" ht="15" customHeight="1">
       <x:c r="A174" s="1" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="B174" s="1" t="s">
         <x:v>287</x:v>
       </x:c>
-      <x:c r="B174" s="1" t="s">
-        <x:v>288</x:v>
-      </x:c>
       <x:c r="C174" s="1" t="s">
-        <x:v>293</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="D174" s="1" t="s">
         <x:v>25</x:v>
@@ -6916,13 +6913,13 @@
     </x:row>
     <x:row r="175" ht="15" customHeight="1">
       <x:c r="A175" s="1" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="B175" s="1" t="s">
         <x:v>287</x:v>
       </x:c>
-      <x:c r="B175" s="1" t="s">
-        <x:v>288</x:v>
-      </x:c>
       <x:c r="C175" s="1" t="s">
-        <x:v>294</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="D175" s="1" t="s">
         <x:v>25</x:v>
@@ -6936,19 +6933,19 @@
     </x:row>
     <x:row r="176" ht="15" customHeight="1">
       <x:c r="A176" s="1" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="B176" s="1" t="s">
         <x:v>287</x:v>
       </x:c>
-      <x:c r="B176" s="1" t="s">
-        <x:v>288</x:v>
-      </x:c>
       <x:c r="C176" s="1" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="D176" s="1" t="s">
         <x:v>295</x:v>
       </x:c>
-      <x:c r="D176" s="1" t="s">
+      <x:c r="E176" s="1" t="s">
         <x:v>296</x:v>
-      </x:c>
-      <x:c r="E176" s="1" t="s">
-        <x:v>297</x:v>
       </x:c>
       <x:c r="F176" s="2" t="str">
         <x:f>""</x:f>
@@ -6956,19 +6953,19 @@
     </x:row>
     <x:row r="177" ht="15" customHeight="1">
       <x:c r="A177" s="1" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="B177" s="1" t="s">
         <x:v>287</x:v>
       </x:c>
-      <x:c r="B177" s="1" t="s">
-        <x:v>288</x:v>
-      </x:c>
       <x:c r="C177" s="1" t="s">
-        <x:v>298</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="D177" s="1" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="E177" s="1" t="s">
         <x:v>296</x:v>
-      </x:c>
-      <x:c r="E177" s="1" t="s">
-        <x:v>297</x:v>
       </x:c>
       <x:c r="F177" s="2" t="str">
         <x:f>""</x:f>
@@ -6976,19 +6973,19 @@
     </x:row>
     <x:row r="178" ht="15" customHeight="1">
       <x:c r="A178" s="1" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="B178" s="1" t="s">
         <x:v>287</x:v>
       </x:c>
-      <x:c r="B178" s="1" t="s">
-        <x:v>288</x:v>
-      </x:c>
       <x:c r="C178" s="1" t="s">
-        <x:v>299</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="D178" s="1" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="E178" s="1" t="s">
         <x:v>296</x:v>
-      </x:c>
-      <x:c r="E178" s="1" t="s">
-        <x:v>297</x:v>
       </x:c>
       <x:c r="F178" s="2" t="str">
         <x:f>""</x:f>
@@ -6996,19 +6993,19 @@
     </x:row>
     <x:row r="179" ht="15" customHeight="1">
       <x:c r="A179" s="1" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="B179" s="1" t="s">
         <x:v>287</x:v>
       </x:c>
-      <x:c r="B179" s="1" t="s">
-        <x:v>288</x:v>
-      </x:c>
       <x:c r="C179" s="1" t="s">
-        <x:v>300</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="D179" s="1" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="E179" s="1" t="s">
         <x:v>296</x:v>
-      </x:c>
-      <x:c r="E179" s="1" t="s">
-        <x:v>297</x:v>
       </x:c>
       <x:c r="F179" s="2" t="str">
         <x:f>""</x:f>
@@ -7016,10 +7013,10 @@
     </x:row>
     <x:row r="180" ht="15" customHeight="1">
       <x:c r="A180" s="1" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="B180" s="1" t="s">
         <x:v>301</x:v>
-      </x:c>
-      <x:c r="B180" s="1" t="s">
-        <x:v>302</x:v>
       </x:c>
       <x:c r="C180" s="1" t="s">
         <x:v>18</x:v>
@@ -7036,10 +7033,10 @@
     </x:row>
     <x:row r="181" ht="15" customHeight="1">
       <x:c r="A181" s="1" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="B181" s="1" t="s">
         <x:v>301</x:v>
-      </x:c>
-      <x:c r="B181" s="1" t="s">
-        <x:v>302</x:v>
       </x:c>
       <x:c r="C181" s="1" t="s">
         <x:v>44</x:v>
@@ -7056,10 +7053,10 @@
     </x:row>
     <x:row r="182" ht="15" customHeight="1">
       <x:c r="A182" s="1" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="B182" s="1" t="s">
         <x:v>301</x:v>
-      </x:c>
-      <x:c r="B182" s="1" t="s">
-        <x:v>302</x:v>
       </x:c>
       <x:c r="C182" s="1" t="s">
         <x:v>41</x:v>
@@ -7076,10 +7073,10 @@
     </x:row>
     <x:row r="183" ht="15" customHeight="1">
       <x:c r="A183" s="1" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="B183" s="1" t="s">
         <x:v>301</x:v>
-      </x:c>
-      <x:c r="B183" s="1" t="s">
-        <x:v>302</x:v>
       </x:c>
       <x:c r="C183" s="1" t="s">
         <x:v>95</x:v>
@@ -7088,7 +7085,7 @@
         <x:v>202</x:v>
       </x:c>
       <x:c r="E183" s="1" t="s">
-        <x:v>303</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="F183" s="2" t="s">
         <x:v>14</x:v>
@@ -7096,10 +7093,10 @@
     </x:row>
     <x:row r="184" ht="15" customHeight="1">
       <x:c r="A184" s="1" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="B184" s="1" t="s">
         <x:v>304</x:v>
-      </x:c>
-      <x:c r="B184" s="1" t="s">
-        <x:v>305</x:v>
       </x:c>
       <x:c r="C184" s="1" t="s">
         <x:v>44</x:v>
@@ -7116,10 +7113,10 @@
     </x:row>
     <x:row r="185" ht="15" customHeight="1">
       <x:c r="A185" s="1" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="B185" s="1" t="s">
         <x:v>304</x:v>
-      </x:c>
-      <x:c r="B185" s="1" t="s">
-        <x:v>305</x:v>
       </x:c>
       <x:c r="C185" s="1" t="s">
         <x:v>41</x:v>
@@ -7128,7 +7125,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="E185" s="1" t="s">
-        <x:v>306</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="F185" s="2" t="s">
         <x:v>14</x:v>
@@ -7136,10 +7133,10 @@
     </x:row>
     <x:row r="186" ht="15" customHeight="1">
       <x:c r="A186" s="1" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="B186" s="1" t="s">
         <x:v>304</x:v>
-      </x:c>
-      <x:c r="B186" s="1" t="s">
-        <x:v>305</x:v>
       </x:c>
       <x:c r="C186" s="1" t="s">
         <x:v>95</x:v>
@@ -7156,19 +7153,19 @@
     </x:row>
     <x:row r="187" ht="15" customHeight="1">
       <x:c r="A187" s="1" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="B187" s="1" t="s">
         <x:v>304</x:v>
-      </x:c>
-      <x:c r="B187" s="1" t="s">
-        <x:v>305</x:v>
       </x:c>
       <x:c r="C187" s="1" t="s">
         <x:v>181</x:v>
       </x:c>
       <x:c r="D187" s="1" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="E187" s="1" t="s">
         <x:v>307</x:v>
-      </x:c>
-      <x:c r="E187" s="1" t="s">
-        <x:v>308</x:v>
       </x:c>
       <x:c r="F187" s="2" t="s">
         <x:v>14</x:v>
@@ -7176,10 +7173,10 @@
     </x:row>
     <x:row r="188" ht="15" customHeight="1">
       <x:c r="A188" s="1" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="B188" s="1" t="s">
         <x:v>304</x:v>
-      </x:c>
-      <x:c r="B188" s="1" t="s">
-        <x:v>305</x:v>
       </x:c>
       <x:c r="C188" s="1" t="s">
         <x:v>18</x:v>
@@ -7196,10 +7193,10 @@
     </x:row>
     <x:row r="189" ht="15" customHeight="1">
       <x:c r="A189" s="1" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="B189" s="1" t="s">
         <x:v>304</x:v>
-      </x:c>
-      <x:c r="B189" s="1" t="s">
-        <x:v>305</x:v>
       </x:c>
       <x:c r="C189" s="1" t="s">
         <x:v>61</x:v>
@@ -7208,7 +7205,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="E189" s="1" t="s">
-        <x:v>309</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="F189" s="2" t="s">
         <x:v>14</x:v>
@@ -7216,10 +7213,10 @@
     </x:row>
     <x:row r="190" ht="15" customHeight="1">
       <x:c r="A190" s="1" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="B190" s="1" t="s">
         <x:v>310</x:v>
-      </x:c>
-      <x:c r="B190" s="1" t="s">
-        <x:v>311</x:v>
       </x:c>
       <x:c r="C190" s="1" t="s">
         <x:v>44</x:v>
@@ -7236,13 +7233,13 @@
     </x:row>
     <x:row r="191" ht="15" customHeight="1">
       <x:c r="A191" s="1" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="B191" s="1" t="s">
         <x:v>310</x:v>
       </x:c>
-      <x:c r="B191" s="1" t="s">
+      <x:c r="C191" s="1" t="s">
         <x:v>311</x:v>
-      </x:c>
-      <x:c r="C191" s="1" t="s">
-        <x:v>312</x:v>
       </x:c>
       <x:c r="D191" s="1" t="s">
         <x:v>25</x:v>
@@ -7256,10 +7253,10 @@
     </x:row>
     <x:row r="192" ht="15" customHeight="1">
       <x:c r="A192" s="1" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="B192" s="1" t="s">
         <x:v>310</x:v>
-      </x:c>
-      <x:c r="B192" s="1" t="s">
-        <x:v>311</x:v>
       </x:c>
       <x:c r="C192" s="1" t="s">
         <x:v>41</x:v>
@@ -7276,10 +7273,10 @@
     </x:row>
     <x:row r="193" ht="15" customHeight="1">
       <x:c r="A193" s="1" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="B193" s="1" t="s">
         <x:v>310</x:v>
-      </x:c>
-      <x:c r="B193" s="1" t="s">
-        <x:v>311</x:v>
       </x:c>
       <x:c r="C193" s="1" t="s">
         <x:v>95</x:v>
@@ -7288,7 +7285,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="E193" s="1" t="s">
-        <x:v>313</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="F193" s="2" t="s">
         <x:v>14</x:v>
@@ -7296,10 +7293,10 @@
     </x:row>
     <x:row r="194" ht="15" customHeight="1">
       <x:c r="A194" s="1" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="B194" s="1" t="s">
         <x:v>310</x:v>
-      </x:c>
-      <x:c r="B194" s="1" t="s">
-        <x:v>311</x:v>
       </x:c>
       <x:c r="C194" s="1" t="s">
         <x:v>181</x:v>
@@ -7308,7 +7305,7 @@
         <x:v>157</x:v>
       </x:c>
       <x:c r="E194" s="1" t="s">
-        <x:v>314</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="F194" s="2" t="s">
         <x:v>14</x:v>
@@ -7316,10 +7313,10 @@
     </x:row>
     <x:row r="195" ht="15" customHeight="1">
       <x:c r="A195" s="1" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="B195" s="1" t="s">
         <x:v>310</x:v>
-      </x:c>
-      <x:c r="B195" s="1" t="s">
-        <x:v>311</x:v>
       </x:c>
       <x:c r="C195" s="1" t="s">
         <x:v>45</x:v>
@@ -7336,10 +7333,10 @@
     </x:row>
     <x:row r="196" ht="15" customHeight="1">
       <x:c r="A196" s="1" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="B196" s="1" t="s">
         <x:v>310</x:v>
-      </x:c>
-      <x:c r="B196" s="1" t="s">
-        <x:v>311</x:v>
       </x:c>
       <x:c r="C196" s="1" t="s">
         <x:v>61</x:v>
@@ -7348,7 +7345,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="E196" s="1" t="s">
-        <x:v>315</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="F196" s="2" t="s">
         <x:v>14</x:v>
@@ -7356,19 +7353,19 @@
     </x:row>
     <x:row r="197" ht="15" customHeight="1">
       <x:c r="A197" s="1" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="B197" s="1" t="s">
         <x:v>310</x:v>
       </x:c>
-      <x:c r="B197" s="1" t="s">
-        <x:v>311</x:v>
-      </x:c>
       <x:c r="C197" s="1" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="D197" s="1" t="s">
         <x:v>316</x:v>
       </x:c>
-      <x:c r="D197" s="1" t="s">
+      <x:c r="E197" s="1" t="s">
         <x:v>317</x:v>
-      </x:c>
-      <x:c r="E197" s="1" t="s">
-        <x:v>318</x:v>
       </x:c>
       <x:c r="F197" s="2" t="s">
         <x:v>14</x:v>
@@ -7376,19 +7373,19 @@
     </x:row>
     <x:row r="198" ht="15" customHeight="1">
       <x:c r="A198" s="1" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="B198" s="1" t="s">
         <x:v>310</x:v>
       </x:c>
-      <x:c r="B198" s="1" t="s">
-        <x:v>311</x:v>
-      </x:c>
       <x:c r="C198" s="1" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="D198" s="1" t="s">
         <x:v>319</x:v>
       </x:c>
-      <x:c r="D198" s="1" t="s">
+      <x:c r="E198" s="1" t="s">
         <x:v>320</x:v>
-      </x:c>
-      <x:c r="E198" s="1" t="s">
-        <x:v>321</x:v>
       </x:c>
       <x:c r="F198" s="2" t="str">
         <x:f>""</x:f>
@@ -7396,19 +7393,19 @@
     </x:row>
     <x:row r="199" ht="15" customHeight="1">
       <x:c r="A199" s="1" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="B199" s="1" t="s">
         <x:v>310</x:v>
-      </x:c>
-      <x:c r="B199" s="1" t="s">
-        <x:v>311</x:v>
       </x:c>
       <x:c r="C199" s="1" t="s">
         <x:v>163</x:v>
       </x:c>
       <x:c r="D199" s="1" t="s">
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="E199" s="1" t="s">
         <x:v>322</x:v>
-      </x:c>
-      <x:c r="E199" s="1" t="s">
-        <x:v>323</x:v>
       </x:c>
       <x:c r="F199" s="2" t="s">
         <x:v>14</x:v>
@@ -7416,10 +7413,10 @@
     </x:row>
     <x:row r="200" ht="15" customHeight="1">
       <x:c r="A200" s="1" t="s">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="B200" s="1" t="s">
         <x:v>324</x:v>
-      </x:c>
-      <x:c r="B200" s="1" t="s">
-        <x:v>325</x:v>
       </x:c>
       <x:c r="C200" s="1" t="s">
         <x:v>44</x:v>
@@ -7436,19 +7433,19 @@
     </x:row>
     <x:row r="201" ht="15" customHeight="1">
       <x:c r="A201" s="1" t="s">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="B201" s="1" t="s">
         <x:v>324</x:v>
-      </x:c>
-      <x:c r="B201" s="1" t="s">
-        <x:v>325</x:v>
       </x:c>
       <x:c r="C201" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="D201" s="1" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="E201" s="1" t="s">
         <x:v>326</x:v>
-      </x:c>
-      <x:c r="E201" s="1" t="s">
-        <x:v>327</x:v>
       </x:c>
       <x:c r="F201" s="2" t="s">
         <x:v>14</x:v>
@@ -7456,10 +7453,10 @@
     </x:row>
     <x:row r="202" ht="15" customHeight="1">
       <x:c r="A202" s="1" t="s">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="B202" s="1" t="s">
         <x:v>328</x:v>
-      </x:c>
-      <x:c r="B202" s="1" t="s">
-        <x:v>329</x:v>
       </x:c>
       <x:c r="C202" s="1" t="s">
         <x:v>44</x:v>
@@ -7476,10 +7473,10 @@
     </x:row>
     <x:row r="203" ht="15" customHeight="1">
       <x:c r="A203" s="1" t="s">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="B203" s="1" t="s">
         <x:v>328</x:v>
-      </x:c>
-      <x:c r="B203" s="1" t="s">
-        <x:v>329</x:v>
       </x:c>
       <x:c r="C203" s="1" t="s">
         <x:v>41</x:v>
@@ -7488,7 +7485,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="E203" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="F203" s="2" t="s">
         <x:v>14</x:v>
@@ -7496,10 +7493,10 @@
     </x:row>
     <x:row r="204" ht="15" customHeight="1">
       <x:c r="A204" s="1" t="s">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="B204" s="1" t="s">
         <x:v>328</x:v>
-      </x:c>
-      <x:c r="B204" s="1" t="s">
-        <x:v>329</x:v>
       </x:c>
       <x:c r="C204" s="1" t="s">
         <x:v>55</x:v>
@@ -7508,7 +7505,7 @@
         <x:v>133</x:v>
       </x:c>
       <x:c r="E204" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="F204" s="2" t="s">
         <x:v>14</x:v>
@@ -7516,10 +7513,10 @@
     </x:row>
     <x:row r="205" ht="15" customHeight="1">
       <x:c r="A205" s="1" t="s">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="B205" s="1" t="s">
         <x:v>328</x:v>
-      </x:c>
-      <x:c r="B205" s="1" t="s">
-        <x:v>329</x:v>
       </x:c>
       <x:c r="C205" s="1" t="s">
         <x:v>45</x:v>
@@ -7528,7 +7525,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="E205" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="F205" s="2" t="s">
         <x:v>14</x:v>
@@ -7536,19 +7533,19 @@
     </x:row>
     <x:row r="206" ht="15" customHeight="1">
       <x:c r="A206" s="1" t="s">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="B206" s="1" t="s">
         <x:v>328</x:v>
       </x:c>
-      <x:c r="B206" s="1" t="s">
-        <x:v>329</x:v>
-      </x:c>
       <x:c r="C206" s="1" t="s">
-        <x:v>333</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="D206" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="E206" s="1" t="s">
-        <x:v>334</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="F206" s="2" t="str">
         <x:f>""</x:f>
@@ -7556,10 +7553,10 @@
     </x:row>
     <x:row r="207" ht="15" customHeight="1">
       <x:c r="A207" s="1" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="B207" s="1" t="s">
         <x:v>335</x:v>
-      </x:c>
-      <x:c r="B207" s="1" t="s">
-        <x:v>336</x:v>
       </x:c>
       <x:c r="C207" s="1" t="s">
         <x:v>44</x:v>
@@ -7576,10 +7573,10 @@
     </x:row>
     <x:row r="208" ht="15" customHeight="1">
       <x:c r="A208" s="1" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="B208" s="1" t="s">
         <x:v>335</x:v>
-      </x:c>
-      <x:c r="B208" s="1" t="s">
-        <x:v>336</x:v>
       </x:c>
       <x:c r="C208" s="1" t="s">
         <x:v>41</x:v>
@@ -7588,7 +7585,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="E208" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="F208" s="2" t="s">
         <x:v>14</x:v>
@@ -7596,10 +7593,10 @@
     </x:row>
     <x:row r="209" ht="15" customHeight="1">
       <x:c r="A209" s="1" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="B209" s="1" t="s">
         <x:v>335</x:v>
-      </x:c>
-      <x:c r="B209" s="1" t="s">
-        <x:v>336</x:v>
       </x:c>
       <x:c r="C209" s="1" t="s">
         <x:v>55</x:v>
@@ -7608,7 +7605,7 @@
         <x:v>133</x:v>
       </x:c>
       <x:c r="E209" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="F209" s="2" t="s">
         <x:v>14</x:v>
@@ -7616,10 +7613,10 @@
     </x:row>
     <x:row r="210" ht="15" customHeight="1">
       <x:c r="A210" s="1" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="B210" s="1" t="s">
         <x:v>335</x:v>
-      </x:c>
-      <x:c r="B210" s="1" t="s">
-        <x:v>336</x:v>
       </x:c>
       <x:c r="C210" s="1" t="s">
         <x:v>45</x:v>
@@ -7628,7 +7625,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="E210" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="F210" s="2" t="s">
         <x:v>14</x:v>
@@ -7636,19 +7633,19 @@
     </x:row>
     <x:row r="211" ht="15" customHeight="1">
       <x:c r="A211" s="1" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="B211" s="1" t="s">
         <x:v>335</x:v>
       </x:c>
-      <x:c r="B211" s="1" t="s">
-        <x:v>336</x:v>
-      </x:c>
       <x:c r="C211" s="1" t="s">
-        <x:v>333</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="D211" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="E211" s="1" t="s">
-        <x:v>334</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="F211" s="2" t="str">
         <x:f>""</x:f>
@@ -7656,10 +7653,10 @@
     </x:row>
     <x:row r="212" ht="15" customHeight="1">
       <x:c r="A212" s="1" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="B212" s="1" t="s">
         <x:v>337</x:v>
-      </x:c>
-      <x:c r="B212" s="1" t="s">
-        <x:v>338</x:v>
       </x:c>
       <x:c r="C212" s="1" t="s">
         <x:v>116</x:v>
@@ -7676,10 +7673,10 @@
     </x:row>
     <x:row r="213" ht="15" customHeight="1">
       <x:c r="A213" s="1" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="B213" s="1" t="s">
         <x:v>337</x:v>
-      </x:c>
-      <x:c r="B213" s="1" t="s">
-        <x:v>338</x:v>
       </x:c>
       <x:c r="C213" s="1" t="s">
         <x:v>118</x:v>
@@ -7696,10 +7693,10 @@
     </x:row>
     <x:row r="214" ht="15" customHeight="1">
       <x:c r="A214" s="1" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="B214" s="1" t="s">
         <x:v>337</x:v>
-      </x:c>
-      <x:c r="B214" s="1" t="s">
-        <x:v>338</x:v>
       </x:c>
       <x:c r="C214" s="1" t="s">
         <x:v>45</x:v>
@@ -7716,10 +7713,10 @@
     </x:row>
     <x:row r="215" ht="15" customHeight="1">
       <x:c r="A215" s="1" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="B215" s="1" t="s">
         <x:v>337</x:v>
-      </x:c>
-      <x:c r="B215" s="1" t="s">
-        <x:v>338</x:v>
       </x:c>
       <x:c r="C215" s="1" t="s">
         <x:v>44</x:v>
@@ -7736,10 +7733,10 @@
     </x:row>
     <x:row r="216" ht="15" customHeight="1">
       <x:c r="A216" s="1" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="B216" s="1" t="s">
         <x:v>337</x:v>
-      </x:c>
-      <x:c r="B216" s="1" t="s">
-        <x:v>338</x:v>
       </x:c>
       <x:c r="C216" s="1" t="s">
         <x:v>86</x:v>
@@ -7756,19 +7753,19 @@
     </x:row>
     <x:row r="217" ht="15" customHeight="1">
       <x:c r="A217" s="1" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="B217" s="1" t="s">
         <x:v>337</x:v>
       </x:c>
-      <x:c r="B217" s="1" t="s">
+      <x:c r="C217" s="1" t="s">
         <x:v>338</x:v>
       </x:c>
-      <x:c r="C217" s="1" t="s">
+      <x:c r="D217" s="1" t="s">
         <x:v>339</x:v>
       </x:c>
-      <x:c r="D217" s="1" t="s">
+      <x:c r="E217" s="1" t="s">
         <x:v>340</x:v>
-      </x:c>
-      <x:c r="E217" s="1" t="s">
-        <x:v>341</x:v>
       </x:c>
       <x:c r="F217" s="2" t="s">
         <x:v>14</x:v>
@@ -7776,10 +7773,10 @@
     </x:row>
     <x:row r="218" ht="15" customHeight="1">
       <x:c r="A218" s="1" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="B218" s="1" t="s">
         <x:v>337</x:v>
-      </x:c>
-      <x:c r="B218" s="1" t="s">
-        <x:v>338</x:v>
       </x:c>
       <x:c r="C218" s="1" t="s">
         <x:v>41</x:v>
@@ -7796,10 +7793,10 @@
     </x:row>
     <x:row r="219" ht="15" customHeight="1">
       <x:c r="A219" s="1" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="B219" s="1" t="s">
         <x:v>337</x:v>
-      </x:c>
-      <x:c r="B219" s="1" t="s">
-        <x:v>338</x:v>
       </x:c>
       <x:c r="C219" s="1" t="s">
         <x:v>120</x:v>
@@ -7816,10 +7813,10 @@
     </x:row>
     <x:row r="220" ht="15" customHeight="1">
       <x:c r="A220" s="1" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="B220" s="1" t="s">
         <x:v>337</x:v>
-      </x:c>
-      <x:c r="B220" s="1" t="s">
-        <x:v>338</x:v>
       </x:c>
       <x:c r="C220" s="1" t="s">
         <x:v>123</x:v>
@@ -7836,10 +7833,10 @@
     </x:row>
     <x:row r="221" ht="15" customHeight="1">
       <x:c r="A221" s="1" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="B221" s="1" t="s">
         <x:v>337</x:v>
-      </x:c>
-      <x:c r="B221" s="1" t="s">
-        <x:v>338</x:v>
       </x:c>
       <x:c r="C221" s="1" t="s">
         <x:v>124</x:v>
@@ -7856,19 +7853,19 @@
     </x:row>
     <x:row r="222" ht="15" customHeight="1">
       <x:c r="A222" s="1" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="B222" s="1" t="s">
         <x:v>337</x:v>
       </x:c>
-      <x:c r="B222" s="1" t="s">
-        <x:v>338</x:v>
-      </x:c>
       <x:c r="C222" s="1" t="s">
-        <x:v>342</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="D222" s="1" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="E222" s="1" t="s">
-        <x:v>343</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="F222" s="2" t="s">
         <x:v>14</x:v>
@@ -7876,19 +7873,19 @@
     </x:row>
     <x:row r="223" ht="15" customHeight="1">
       <x:c r="A223" s="1" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="B223" s="1" t="s">
         <x:v>344</x:v>
       </x:c>
-      <x:c r="B223" s="1" t="s">
+      <x:c r="C223" s="1" t="s">
         <x:v>345</x:v>
       </x:c>
-      <x:c r="C223" s="1" t="s">
+      <x:c r="D223" s="1" t="s">
         <x:v>346</x:v>
       </x:c>
-      <x:c r="D223" s="1" t="s">
+      <x:c r="E223" s="1" t="s">
         <x:v>347</x:v>
-      </x:c>
-      <x:c r="E223" s="1" t="s">
-        <x:v>348</x:v>
       </x:c>
       <x:c r="F223" s="2" t="str">
         <x:f>""</x:f>
@@ -7896,19 +7893,19 @@
     </x:row>
     <x:row r="224" ht="15" customHeight="1">
       <x:c r="A224" s="1" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="B224" s="1" t="s">
         <x:v>344</x:v>
       </x:c>
-      <x:c r="B224" s="1" t="s">
-        <x:v>345</x:v>
-      </x:c>
       <x:c r="C224" s="1" t="s">
-        <x:v>349</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="D224" s="1" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="E224" s="1" t="s">
         <x:v>347</x:v>
-      </x:c>
-      <x:c r="E224" s="1" t="s">
-        <x:v>348</x:v>
       </x:c>
       <x:c r="F224" s="2" t="str">
         <x:f>""</x:f>
@@ -7916,19 +7913,19 @@
     </x:row>
     <x:row r="225" ht="15" customHeight="1">
       <x:c r="A225" s="1" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="B225" s="1" t="s">
         <x:v>344</x:v>
       </x:c>
-      <x:c r="B225" s="1" t="s">
-        <x:v>345</x:v>
-      </x:c>
       <x:c r="C225" s="1" t="s">
-        <x:v>350</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="D225" s="1" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="E225" s="1" t="s">
         <x:v>347</x:v>
-      </x:c>
-      <x:c r="E225" s="1" t="s">
-        <x:v>348</x:v>
       </x:c>
       <x:c r="F225" s="2" t="str">
         <x:f>""</x:f>
@@ -7936,19 +7933,19 @@
     </x:row>
     <x:row r="226" ht="15" customHeight="1">
       <x:c r="A226" s="1" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="B226" s="1" t="s">
         <x:v>344</x:v>
       </x:c>
-      <x:c r="B226" s="1" t="s">
-        <x:v>345</x:v>
-      </x:c>
       <x:c r="C226" s="1" t="s">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="D226" s="1" t="s">
         <x:v>351</x:v>
       </x:c>
-      <x:c r="D226" s="1" t="s">
+      <x:c r="E226" s="1" t="s">
         <x:v>352</x:v>
-      </x:c>
-      <x:c r="E226" s="1" t="s">
-        <x:v>353</x:v>
       </x:c>
       <x:c r="F226" s="2" t="str">
         <x:f>""</x:f>
@@ -7956,19 +7953,19 @@
     </x:row>
     <x:row r="227" ht="15" customHeight="1">
       <x:c r="A227" s="1" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="B227" s="1" t="s">
         <x:v>344</x:v>
       </x:c>
-      <x:c r="B227" s="1" t="s">
-        <x:v>345</x:v>
-      </x:c>
       <x:c r="C227" s="1" t="s">
-        <x:v>354</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="D227" s="1" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="E227" s="1" t="s">
         <x:v>347</x:v>
-      </x:c>
-      <x:c r="E227" s="1" t="s">
-        <x:v>348</x:v>
       </x:c>
       <x:c r="F227" s="2" t="str">
         <x:f>""</x:f>
@@ -7976,13 +7973,13 @@
     </x:row>
     <x:row r="228" ht="15" customHeight="1">
       <x:c r="A228" s="1" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="B228" s="1" t="s">
         <x:v>344</x:v>
       </x:c>
-      <x:c r="B228" s="1" t="s">
-        <x:v>345</x:v>
-      </x:c>
       <x:c r="C228" s="1" t="s">
-        <x:v>355</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="D228" s="1" t="s">
         <x:v>38</x:v>
@@ -7996,13 +7993,13 @@
     </x:row>
     <x:row r="229" ht="15" customHeight="1">
       <x:c r="A229" s="1" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="B229" s="1" t="s">
         <x:v>344</x:v>
       </x:c>
-      <x:c r="B229" s="1" t="s">
-        <x:v>345</x:v>
-      </x:c>
       <x:c r="C229" s="1" t="s">
-        <x:v>356</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="D229" s="1" t="s">
         <x:v>38</x:v>
@@ -8016,13 +8013,13 @@
     </x:row>
     <x:row r="230" ht="15" customHeight="1">
       <x:c r="A230" s="1" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="B230" s="1" t="s">
         <x:v>344</x:v>
       </x:c>
-      <x:c r="B230" s="1" t="s">
-        <x:v>345</x:v>
-      </x:c>
       <x:c r="C230" s="1" t="s">
-        <x:v>357</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="D230" s="1" t="s">
         <x:v>38</x:v>
@@ -8036,13 +8033,13 @@
     </x:row>
     <x:row r="231" ht="15" customHeight="1">
       <x:c r="A231" s="1" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="B231" s="1" t="s">
         <x:v>344</x:v>
       </x:c>
-      <x:c r="B231" s="1" t="s">
-        <x:v>345</x:v>
-      </x:c>
       <x:c r="C231" s="1" t="s">
-        <x:v>358</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="D231" s="1" t="s">
         <x:v>38</x:v>
@@ -8056,19 +8053,19 @@
     </x:row>
     <x:row r="232" ht="15" customHeight="1">
       <x:c r="A232" s="1" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="B232" s="1" t="s">
         <x:v>344</x:v>
       </x:c>
-      <x:c r="B232" s="1" t="s">
-        <x:v>345</x:v>
-      </x:c>
       <x:c r="C232" s="1" t="s">
+        <x:v>358</x:v>
+      </x:c>
+      <x:c r="D232" s="1" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="E232" s="1" t="s">
         <x:v>359</x:v>
-      </x:c>
-      <x:c r="D232" s="1" t="s">
-        <x:v>289</x:v>
-      </x:c>
-      <x:c r="E232" s="1" t="s">
-        <x:v>360</x:v>
       </x:c>
       <x:c r="F232" s="2" t="s">
         <x:v>14</x:v>
@@ -8076,13 +8073,13 @@
     </x:row>
     <x:row r="233" ht="15" customHeight="1">
       <x:c r="A233" s="1" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="B233" s="1" t="s">
         <x:v>344</x:v>
       </x:c>
-      <x:c r="B233" s="1" t="s">
-        <x:v>345</x:v>
-      </x:c>
       <x:c r="C233" s="1" t="s">
-        <x:v>361</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="D233" s="1" t="s">
         <x:v>25</x:v>
@@ -8096,10 +8093,10 @@
     </x:row>
     <x:row r="234" ht="15" customHeight="1">
       <x:c r="A234" s="1" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="B234" s="1" t="s">
         <x:v>344</x:v>
-      </x:c>
-      <x:c r="B234" s="1" t="s">
-        <x:v>345</x:v>
       </x:c>
       <x:c r="C234" s="1" t="s">
         <x:v>18</x:v>
@@ -8116,19 +8113,19 @@
     </x:row>
     <x:row r="235" ht="15" customHeight="1">
       <x:c r="A235" s="1" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="B235" s="1" t="s">
         <x:v>344</x:v>
-      </x:c>
-      <x:c r="B235" s="1" t="s">
-        <x:v>345</x:v>
       </x:c>
       <x:c r="C235" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
       <x:c r="D235" s="1" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="E235" s="1" t="s">
         <x:v>362</x:v>
-      </x:c>
-      <x:c r="E235" s="1" t="s">
-        <x:v>363</x:v>
       </x:c>
       <x:c r="F235" s="2" t="s">
         <x:v>14</x:v>
@@ -8136,10 +8133,10 @@
     </x:row>
     <x:row r="236" ht="15" customHeight="1">
       <x:c r="A236" s="1" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="B236" s="1" t="s">
         <x:v>344</x:v>
-      </x:c>
-      <x:c r="B236" s="1" t="s">
-        <x:v>345</x:v>
       </x:c>
       <x:c r="C236" s="1" t="s">
         <x:v>86</x:v>
@@ -8156,19 +8153,19 @@
     </x:row>
     <x:row r="237" ht="15" customHeight="1">
       <x:c r="A237" s="1" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="B237" s="1" t="s">
         <x:v>344</x:v>
       </x:c>
-      <x:c r="B237" s="1" t="s">
-        <x:v>345</x:v>
-      </x:c>
       <x:c r="C237" s="1" t="s">
+        <x:v>363</x:v>
+      </x:c>
+      <x:c r="D237" s="1" t="s">
         <x:v>364</x:v>
       </x:c>
-      <x:c r="D237" s="1" t="s">
+      <x:c r="E237" s="1" t="s">
         <x:v>365</x:v>
-      </x:c>
-      <x:c r="E237" s="1" t="s">
-        <x:v>366</x:v>
       </x:c>
       <x:c r="F237" s="2" t="s">
         <x:v>14</x:v>
@@ -8176,10 +8173,10 @@
     </x:row>
     <x:row r="238" ht="15" customHeight="1">
       <x:c r="A238" s="1" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="B238" s="1" t="s">
         <x:v>344</x:v>
-      </x:c>
-      <x:c r="B238" s="1" t="s">
-        <x:v>345</x:v>
       </x:c>
       <x:c r="C238" s="1" t="s">
         <x:v>124</x:v>
@@ -8196,13 +8193,13 @@
     </x:row>
     <x:row r="239" ht="15" customHeight="1">
       <x:c r="A239" s="1" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="B239" s="1" t="s">
         <x:v>344</x:v>
       </x:c>
-      <x:c r="B239" s="1" t="s">
-        <x:v>345</x:v>
-      </x:c>
       <x:c r="C239" s="1" t="s">
-        <x:v>367</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="D239" s="1" t="s">
         <x:v>16</x:v>
@@ -8216,19 +8213,19 @@
     </x:row>
     <x:row r="240" ht="15" customHeight="1">
       <x:c r="A240" s="1" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="B240" s="1" t="s">
         <x:v>344</x:v>
       </x:c>
-      <x:c r="B240" s="1" t="s">
-        <x:v>345</x:v>
-      </x:c>
       <x:c r="C240" s="1" t="s">
+        <x:v>367</x:v>
+      </x:c>
+      <x:c r="D240" s="1" t="s">
         <x:v>368</x:v>
       </x:c>
-      <x:c r="D240" s="1" t="s">
+      <x:c r="E240" s="1" t="s">
         <x:v>369</x:v>
-      </x:c>
-      <x:c r="E240" s="1" t="s">
-        <x:v>370</x:v>
       </x:c>
       <x:c r="F240" s="2" t="s">
         <x:v>14</x:v>
@@ -8236,10 +8233,10 @@
     </x:row>
     <x:row r="241" ht="15" customHeight="1">
       <x:c r="A241" s="1" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="B241" s="1" t="s">
         <x:v>371</x:v>
-      </x:c>
-      <x:c r="B241" s="1" t="s">
-        <x:v>372</x:v>
       </x:c>
       <x:c r="C241" s="1" t="s">
         <x:v>44</x:v>
@@ -8256,10 +8253,10 @@
     </x:row>
     <x:row r="242" ht="15" customHeight="1">
       <x:c r="A242" s="1" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="B242" s="1" t="s">
         <x:v>371</x:v>
-      </x:c>
-      <x:c r="B242" s="1" t="s">
-        <x:v>372</x:v>
       </x:c>
       <x:c r="C242" s="1" t="s">
         <x:v>41</x:v>
@@ -8268,7 +8265,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="E242" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="F242" s="2" t="s">
         <x:v>14</x:v>
@@ -8276,19 +8273,19 @@
     </x:row>
     <x:row r="243" ht="15" customHeight="1">
       <x:c r="A243" s="1" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="B243" s="1" t="s">
         <x:v>371</x:v>
       </x:c>
-      <x:c r="B243" s="1" t="s">
+      <x:c r="C243" s="1" t="s">
         <x:v>372</x:v>
       </x:c>
-      <x:c r="C243" s="1" t="s">
+      <x:c r="D243" s="1" t="s">
         <x:v>373</x:v>
       </x:c>
-      <x:c r="D243" s="1" t="s">
+      <x:c r="E243" s="1" t="s">
         <x:v>374</x:v>
-      </x:c>
-      <x:c r="E243" s="1" t="s">
-        <x:v>375</x:v>
       </x:c>
       <x:c r="F243" s="2" t="s">
         <x:v>14</x:v>
@@ -8296,10 +8293,10 @@
     </x:row>
     <x:row r="244" ht="15" customHeight="1">
       <x:c r="A244" s="1" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="B244" s="1" t="s">
         <x:v>371</x:v>
-      </x:c>
-      <x:c r="B244" s="1" t="s">
-        <x:v>372</x:v>
       </x:c>
       <x:c r="C244" s="1" t="s">
         <x:v>45</x:v>
@@ -8316,19 +8313,19 @@
     </x:row>
     <x:row r="245" ht="15" customHeight="1">
       <x:c r="A245" s="1" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="B245" s="1" t="s">
         <x:v>371</x:v>
       </x:c>
-      <x:c r="B245" s="1" t="s">
-        <x:v>372</x:v>
-      </x:c>
       <x:c r="C245" s="1" t="s">
-        <x:v>376</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="D245" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E245" s="1" t="s">
-        <x:v>377</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="F245" s="2" t="str">
         <x:f>""</x:f>
@@ -8336,13 +8333,13 @@
     </x:row>
     <x:row r="246" ht="15" customHeight="1">
       <x:c r="A246" s="1" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="B246" s="1" t="s">
         <x:v>371</x:v>
       </x:c>
-      <x:c r="B246" s="1" t="s">
-        <x:v>372</x:v>
-      </x:c>
       <x:c r="C246" s="1" t="s">
-        <x:v>378</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="D246" s="1" t="s">
         <x:v>16</x:v>
@@ -8356,19 +8353,19 @@
     </x:row>
     <x:row r="247" ht="15" customHeight="1">
       <x:c r="A247" s="1" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="B247" s="1" t="s">
         <x:v>371</x:v>
       </x:c>
-      <x:c r="B247" s="1" t="s">
-        <x:v>372</x:v>
-      </x:c>
       <x:c r="C247" s="1" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="D247" s="1" t="s">
         <x:v>379</x:v>
       </x:c>
-      <x:c r="D247" s="1" t="s">
+      <x:c r="E247" s="1" t="s">
         <x:v>380</x:v>
-      </x:c>
-      <x:c r="E247" s="1" t="s">
-        <x:v>381</x:v>
       </x:c>
       <x:c r="F247" s="2" t="s">
         <x:v>14</x:v>
@@ -8376,13 +8373,13 @@
     </x:row>
     <x:row r="248" ht="15" customHeight="1">
       <x:c r="A248" s="1" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="B248" s="1" t="s">
         <x:v>371</x:v>
       </x:c>
-      <x:c r="B248" s="1" t="s">
-        <x:v>372</x:v>
-      </x:c>
       <x:c r="C248" s="1" t="s">
-        <x:v>382</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="D248" s="1" t="s">
         <x:v>16</x:v>
@@ -8396,19 +8393,19 @@
     </x:row>
     <x:row r="249" ht="15" customHeight="1">
       <x:c r="A249" s="1" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="B249" s="1" t="s">
         <x:v>371</x:v>
       </x:c>
-      <x:c r="B249" s="1" t="s">
-        <x:v>372</x:v>
-      </x:c>
       <x:c r="C249" s="1" t="s">
-        <x:v>383</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D249" s="1" t="s">
         <x:v>108</x:v>
       </x:c>
       <x:c r="E249" s="1" t="s">
-        <x:v>384</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="F249" s="2" t="s">
         <x:v>14</x:v>
@@ -8416,13 +8413,13 @@
     </x:row>
     <x:row r="250" ht="15" customHeight="1">
       <x:c r="A250" s="1" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="B250" s="1" t="s">
         <x:v>371</x:v>
       </x:c>
-      <x:c r="B250" s="1" t="s">
-        <x:v>372</x:v>
-      </x:c>
       <x:c r="C250" s="1" t="s">
-        <x:v>385</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="D250" s="1" t="s">
         <x:v>25</x:v>
@@ -8436,13 +8433,13 @@
     </x:row>
     <x:row r="251" ht="15" customHeight="1">
       <x:c r="A251" s="1" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="B251" s="1" t="s">
         <x:v>371</x:v>
       </x:c>
-      <x:c r="B251" s="1" t="s">
-        <x:v>372</x:v>
-      </x:c>
       <x:c r="C251" s="1" t="s">
-        <x:v>386</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="D251" s="1" t="s">
         <x:v>16</x:v>
@@ -8456,10 +8453,10 @@
     </x:row>
     <x:row r="252" ht="15" customHeight="1">
       <x:c r="A252" s="1" t="s">
+        <x:v>386</x:v>
+      </x:c>
+      <x:c r="B252" s="1" t="s">
         <x:v>387</x:v>
-      </x:c>
-      <x:c r="B252" s="1" t="s">
-        <x:v>388</x:v>
       </x:c>
       <x:c r="C252" s="1" t="s">
         <x:v>18</x:v>
@@ -8476,10 +8473,10 @@
     </x:row>
     <x:row r="253" ht="15" customHeight="1">
       <x:c r="A253" s="1" t="s">
+        <x:v>386</x:v>
+      </x:c>
+      <x:c r="B253" s="1" t="s">
         <x:v>387</x:v>
-      </x:c>
-      <x:c r="B253" s="1" t="s">
-        <x:v>388</x:v>
       </x:c>
       <x:c r="C253" s="1" t="s">
         <x:v>150</x:v>
@@ -8496,10 +8493,10 @@
     </x:row>
     <x:row r="254" ht="15" customHeight="1">
       <x:c r="A254" s="1" t="s">
+        <x:v>386</x:v>
+      </x:c>
+      <x:c r="B254" s="1" t="s">
         <x:v>387</x:v>
-      </x:c>
-      <x:c r="B254" s="1" t="s">
-        <x:v>388</x:v>
       </x:c>
       <x:c r="C254" s="1" t="s">
         <x:v>152</x:v>
@@ -8516,10 +8513,10 @@
     </x:row>
     <x:row r="255" ht="15" customHeight="1">
       <x:c r="A255" s="1" t="s">
+        <x:v>386</x:v>
+      </x:c>
+      <x:c r="B255" s="1" t="s">
         <x:v>387</x:v>
-      </x:c>
-      <x:c r="B255" s="1" t="s">
-        <x:v>388</x:v>
       </x:c>
       <x:c r="C255" s="1" t="s">
         <x:v>44</x:v>
@@ -8536,10 +8533,10 @@
     </x:row>
     <x:row r="256" ht="15" customHeight="1">
       <x:c r="A256" s="1" t="s">
+        <x:v>386</x:v>
+      </x:c>
+      <x:c r="B256" s="1" t="s">
         <x:v>387</x:v>
-      </x:c>
-      <x:c r="B256" s="1" t="s">
-        <x:v>388</x:v>
       </x:c>
       <x:c r="C256" s="1" t="s">
         <x:v>41</x:v>
@@ -8556,10 +8553,10 @@
     </x:row>
     <x:row r="257" ht="15" customHeight="1">
       <x:c r="A257" s="1" t="s">
+        <x:v>386</x:v>
+      </x:c>
+      <x:c r="B257" s="1" t="s">
         <x:v>387</x:v>
-      </x:c>
-      <x:c r="B257" s="1" t="s">
-        <x:v>388</x:v>
       </x:c>
       <x:c r="C257" s="1" t="s">
         <x:v>156</x:v>
@@ -8576,10 +8573,10 @@
     </x:row>
     <x:row r="258" ht="15" customHeight="1">
       <x:c r="A258" s="1" t="s">
+        <x:v>386</x:v>
+      </x:c>
+      <x:c r="B258" s="1" t="s">
         <x:v>387</x:v>
-      </x:c>
-      <x:c r="B258" s="1" t="s">
-        <x:v>388</x:v>
       </x:c>
       <x:c r="C258" s="1" t="s">
         <x:v>159</x:v>
@@ -8596,13 +8593,13 @@
     </x:row>
     <x:row r="259" ht="15" customHeight="1">
       <x:c r="A259" s="1" t="s">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="B259" s="1" t="s">
         <x:v>389</x:v>
       </x:c>
-      <x:c r="B259" s="1" t="s">
+      <x:c r="C259" s="1" t="s">
         <x:v>390</x:v>
-      </x:c>
-      <x:c r="C259" s="1" t="s">
-        <x:v>391</x:v>
       </x:c>
       <x:c r="D259" s="1" t="s">
         <x:v>238</x:v>
@@ -8616,19 +8613,19 @@
     </x:row>
     <x:row r="260" ht="15" customHeight="1">
       <x:c r="A260" s="1" t="s">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="B260" s="1" t="s">
         <x:v>389</x:v>
       </x:c>
-      <x:c r="B260" s="1" t="s">
-        <x:v>390</x:v>
-      </x:c>
       <x:c r="C260" s="1" t="s">
+        <x:v>391</x:v>
+      </x:c>
+      <x:c r="D260" s="1" t="s">
         <x:v>392</x:v>
       </x:c>
-      <x:c r="D260" s="1" t="s">
+      <x:c r="E260" s="1" t="s">
         <x:v>393</x:v>
-      </x:c>
-      <x:c r="E260" s="1" t="s">
-        <x:v>394</x:v>
       </x:c>
       <x:c r="F260" s="2" t="s">
         <x:v>14</x:v>
@@ -8636,19 +8633,19 @@
     </x:row>
     <x:row r="261" ht="15" customHeight="1">
       <x:c r="A261" s="1" t="s">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="B261" s="1" t="s">
         <x:v>389</x:v>
       </x:c>
-      <x:c r="B261" s="1" t="s">
-        <x:v>390</x:v>
-      </x:c>
       <x:c r="C261" s="1" t="s">
+        <x:v>394</x:v>
+      </x:c>
+      <x:c r="D261" s="1" t="s">
         <x:v>395</x:v>
       </x:c>
-      <x:c r="D261" s="1" t="s">
+      <x:c r="E261" s="1" t="s">
         <x:v>396</x:v>
-      </x:c>
-      <x:c r="E261" s="1" t="s">
-        <x:v>397</x:v>
       </x:c>
       <x:c r="F261" s="2" t="str">
         <x:f>""</x:f>
@@ -8656,19 +8653,19 @@
     </x:row>
     <x:row r="262" ht="15" customHeight="1">
       <x:c r="A262" s="1" t="s">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="B262" s="1" t="s">
         <x:v>389</x:v>
       </x:c>
-      <x:c r="B262" s="1" t="s">
-        <x:v>390</x:v>
-      </x:c>
       <x:c r="C262" s="1" t="s">
-        <x:v>398</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="D262" s="1" t="s">
+        <x:v>395</x:v>
+      </x:c>
+      <x:c r="E262" s="1" t="s">
         <x:v>396</x:v>
-      </x:c>
-      <x:c r="E262" s="1" t="s">
-        <x:v>397</x:v>
       </x:c>
       <x:c r="F262" s="2" t="str">
         <x:f>""</x:f>
@@ -8676,10 +8673,10 @@
     </x:row>
     <x:row r="263" ht="15" customHeight="1">
       <x:c r="A263" s="1" t="s">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="B263" s="1" t="s">
         <x:v>389</x:v>
-      </x:c>
-      <x:c r="B263" s="1" t="s">
-        <x:v>390</x:v>
       </x:c>
       <x:c r="C263" s="1" t="s">
         <x:v>234</x:v>
@@ -8696,19 +8693,19 @@
     </x:row>
     <x:row r="264" ht="15" customHeight="1">
       <x:c r="A264" s="1" t="s">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="B264" s="1" t="s">
         <x:v>389</x:v>
       </x:c>
-      <x:c r="B264" s="1" t="s">
-        <x:v>390</x:v>
-      </x:c>
       <x:c r="C264" s="1" t="s">
-        <x:v>399</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="D264" s="1" t="s">
         <x:v>70</x:v>
       </x:c>
       <x:c r="E264" s="1" t="s">
-        <x:v>400</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="F264" s="2" t="s">
         <x:v>14</x:v>
@@ -8716,19 +8713,19 @@
     </x:row>
     <x:row r="265" ht="15" customHeight="1">
       <x:c r="A265" s="1" t="s">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="B265" s="1" t="s">
         <x:v>389</x:v>
-      </x:c>
-      <x:c r="B265" s="1" t="s">
-        <x:v>390</x:v>
       </x:c>
       <x:c r="C265" s="1" t="s">
         <x:v>229</x:v>
       </x:c>
       <x:c r="D265" s="1" t="s">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="E265" s="1" t="s">
         <x:v>401</x:v>
-      </x:c>
-      <x:c r="E265" s="1" t="s">
-        <x:v>402</x:v>
       </x:c>
       <x:c r="F265" s="2" t="s">
         <x:v>14</x:v>
@@ -8736,19 +8733,19 @@
     </x:row>
     <x:row r="266" ht="15" customHeight="1">
       <x:c r="A266" s="1" t="s">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="B266" s="1" t="s">
         <x:v>389</x:v>
       </x:c>
-      <x:c r="B266" s="1" t="s">
-        <x:v>390</x:v>
-      </x:c>
       <x:c r="C266" s="1" t="s">
+        <x:v>402</x:v>
+      </x:c>
+      <x:c r="D266" s="1" t="s">
         <x:v>403</x:v>
       </x:c>
-      <x:c r="D266" s="1" t="s">
+      <x:c r="E266" s="1" t="s">
         <x:v>404</x:v>
-      </x:c>
-      <x:c r="E266" s="1" t="s">
-        <x:v>405</x:v>
       </x:c>
       <x:c r="F266" s="2" t="str">
         <x:f>""</x:f>
@@ -8756,31 +8753,31 @@
     </x:row>
     <x:row r="267" ht="15" customHeight="1">
       <x:c r="A267" s="1" t="s">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="B267" s="1" t="s">
         <x:v>389</x:v>
       </x:c>
-      <x:c r="B267" s="1" t="s">
-        <x:v>390</x:v>
-      </x:c>
       <x:c r="C267" s="1" t="s">
+        <x:v>405</x:v>
+      </x:c>
+      <x:c r="D267" s="1" t="s">
         <x:v>406</x:v>
       </x:c>
-      <x:c r="D267" s="1" t="s">
+      <x:c r="E267" s="1" t="s">
         <x:v>407</x:v>
-      </x:c>
-      <x:c r="E267" s="1" t="s">
-        <x:v>408</x:v>
       </x:c>
       <x:c r="F267" s="2"/>
     </x:row>
     <x:row r="268" ht="15" customHeight="1">
       <x:c r="A268" s="1" t="s">
+        <x:v>408</x:v>
+      </x:c>
+      <x:c r="B268" s="1" t="s">
         <x:v>409</x:v>
       </x:c>
-      <x:c r="B268" s="1" t="s">
-        <x:v>410</x:v>
-      </x:c>
       <x:c r="C268" s="1" t="s">
-        <x:v>391</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="D268" s="1" t="s">
         <x:v>238</x:v>
@@ -8794,19 +8791,19 @@
     </x:row>
     <x:row r="269" ht="15" customHeight="1">
       <x:c r="A269" s="1" t="s">
+        <x:v>408</x:v>
+      </x:c>
+      <x:c r="B269" s="1" t="s">
         <x:v>409</x:v>
       </x:c>
-      <x:c r="B269" s="1" t="s">
-        <x:v>410</x:v>
-      </x:c>
       <x:c r="C269" s="1" t="s">
+        <x:v>391</x:v>
+      </x:c>
+      <x:c r="D269" s="1" t="s">
         <x:v>392</x:v>
       </x:c>
-      <x:c r="D269" s="1" t="s">
+      <x:c r="E269" s="1" t="s">
         <x:v>393</x:v>
-      </x:c>
-      <x:c r="E269" s="1" t="s">
-        <x:v>394</x:v>
       </x:c>
       <x:c r="F269" s="2" t="s">
         <x:v>14</x:v>
@@ -8814,19 +8811,19 @@
     </x:row>
     <x:row r="270" ht="15" customHeight="1">
       <x:c r="A270" s="1" t="s">
+        <x:v>408</x:v>
+      </x:c>
+      <x:c r="B270" s="1" t="s">
         <x:v>409</x:v>
       </x:c>
-      <x:c r="B270" s="1" t="s">
-        <x:v>410</x:v>
-      </x:c>
       <x:c r="C270" s="1" t="s">
+        <x:v>394</x:v>
+      </x:c>
+      <x:c r="D270" s="1" t="s">
         <x:v>395</x:v>
       </x:c>
-      <x:c r="D270" s="1" t="s">
+      <x:c r="E270" s="1" t="s">
         <x:v>396</x:v>
-      </x:c>
-      <x:c r="E270" s="1" t="s">
-        <x:v>397</x:v>
       </x:c>
       <x:c r="F270" s="2" t="str">
         <x:f>""</x:f>
@@ -8834,19 +8831,19 @@
     </x:row>
     <x:row r="271" ht="15" customHeight="1">
       <x:c r="A271" s="1" t="s">
+        <x:v>408</x:v>
+      </x:c>
+      <x:c r="B271" s="1" t="s">
         <x:v>409</x:v>
       </x:c>
-      <x:c r="B271" s="1" t="s">
-        <x:v>410</x:v>
-      </x:c>
       <x:c r="C271" s="1" t="s">
-        <x:v>398</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="D271" s="1" t="s">
+        <x:v>395</x:v>
+      </x:c>
+      <x:c r="E271" s="1" t="s">
         <x:v>396</x:v>
-      </x:c>
-      <x:c r="E271" s="1" t="s">
-        <x:v>397</x:v>
       </x:c>
       <x:c r="F271" s="2" t="str">
         <x:f>""</x:f>
@@ -8854,10 +8851,10 @@
     </x:row>
     <x:row r="272" ht="15" customHeight="1">
       <x:c r="A272" s="1" t="s">
+        <x:v>408</x:v>
+      </x:c>
+      <x:c r="B272" s="1" t="s">
         <x:v>409</x:v>
-      </x:c>
-      <x:c r="B272" s="1" t="s">
-        <x:v>410</x:v>
       </x:c>
       <x:c r="C272" s="1" t="s">
         <x:v>234</x:v>
@@ -8874,19 +8871,19 @@
     </x:row>
     <x:row r="273" ht="15" customHeight="1">
       <x:c r="A273" s="1" t="s">
+        <x:v>408</x:v>
+      </x:c>
+      <x:c r="B273" s="1" t="s">
         <x:v>409</x:v>
       </x:c>
-      <x:c r="B273" s="1" t="s">
-        <x:v>410</x:v>
-      </x:c>
       <x:c r="C273" s="1" t="s">
-        <x:v>399</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="D273" s="1" t="s">
         <x:v>70</x:v>
       </x:c>
       <x:c r="E273" s="1" t="s">
-        <x:v>400</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="F273" s="2" t="s">
         <x:v>14</x:v>
@@ -8894,19 +8891,19 @@
     </x:row>
     <x:row r="274" ht="15" customHeight="1">
       <x:c r="A274" s="1" t="s">
+        <x:v>408</x:v>
+      </x:c>
+      <x:c r="B274" s="1" t="s">
         <x:v>409</x:v>
-      </x:c>
-      <x:c r="B274" s="1" t="s">
-        <x:v>410</x:v>
       </x:c>
       <x:c r="C274" s="1" t="s">
         <x:v>229</x:v>
       </x:c>
       <x:c r="D274" s="1" t="s">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="E274" s="1" t="s">
         <x:v>401</x:v>
-      </x:c>
-      <x:c r="E274" s="1" t="s">
-        <x:v>402</x:v>
       </x:c>
       <x:c r="F274" s="2" t="s">
         <x:v>14</x:v>
@@ -8914,19 +8911,19 @@
     </x:row>
     <x:row r="275" ht="15" customHeight="1">
       <x:c r="A275" s="1" t="s">
+        <x:v>408</x:v>
+      </x:c>
+      <x:c r="B275" s="1" t="s">
         <x:v>409</x:v>
       </x:c>
-      <x:c r="B275" s="1" t="s">
-        <x:v>410</x:v>
-      </x:c>
       <x:c r="C275" s="1" t="s">
+        <x:v>402</x:v>
+      </x:c>
+      <x:c r="D275" s="1" t="s">
         <x:v>403</x:v>
       </x:c>
-      <x:c r="D275" s="1" t="s">
+      <x:c r="E275" s="1" t="s">
         <x:v>404</x:v>
-      </x:c>
-      <x:c r="E275" s="1" t="s">
-        <x:v>405</x:v>
       </x:c>
       <x:c r="F275" s="2" t="str">
         <x:f>""</x:f>
@@ -8934,26 +8931,26 @@
     </x:row>
     <x:row r="276" ht="15" customHeight="1">
       <x:c r="A276" s="1" t="s">
+        <x:v>408</x:v>
+      </x:c>
+      <x:c r="B276" s="1" t="s">
         <x:v>409</x:v>
       </x:c>
-      <x:c r="B276" s="1" t="s">
-        <x:v>410</x:v>
-      </x:c>
       <x:c r="C276" s="1" t="s">
+        <x:v>405</x:v>
+      </x:c>
+      <x:c r="D276" s="1" t="s">
         <x:v>406</x:v>
       </x:c>
-      <x:c r="D276" s="1" t="s">
+      <x:c r="E276" s="1" t="s">
         <x:v>407</x:v>
-      </x:c>
-      <x:c r="E276" s="1" t="s">
-        <x:v>408</x:v>
       </x:c>
       <x:c r="F276" s="2"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1d7f098bcf304166"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb1b3ad6b3d974601"/>
   </x:tableParts>
 </x:worksheet>
 </file>